--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uidt0706\Documents\UiPath\EU_DE_RBG_ANS_SCM_UploadPickupConfirmation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0B29555-A231-406A-990E-4DB8AFEC955C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7A6840-3FD3-4C47-9D35-4B14710A8C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3405" yWindow="1410" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4920" yWindow="4440" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
     <sheet name="Constants" sheetId="2" r:id="rId2"/>
     <sheet name="Assets" sheetId="3" r:id="rId3"/>
     <sheet name="Credentials" sheetId="4" r:id="rId4"/>
+    <sheet name="Infos" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
   <si>
     <t>Name</t>
   </si>
@@ -160,9 +161,6 @@
     <t xml:space="preserve">The maximum number of consecutive system exceptions was reached. </t>
   </si>
   <si>
-    <t>AUTO/AN/Regensburg/SCM</t>
-  </si>
-  <si>
     <t>OrchestratorQueueName2</t>
   </si>
   <si>
@@ -170,6 +168,15 @@
   </si>
   <si>
     <t>EU_DE_RBG_ANS_SCM_UploadPickupConfirmationSAP</t>
+  </si>
+  <si>
+    <t>AUTO/AN/Regensburg/SCM/LC3</t>
+  </si>
+  <si>
+    <t>Hardcode:</t>
+  </si>
+  <si>
+    <t>Microsoft365 Scope</t>
   </si>
 </sst>
 </file>
@@ -241,10 +248,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -615,7 +622,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>22</v>
@@ -626,7 +633,7 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>32</v>
@@ -647,10 +654,10 @@
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>22</v>
@@ -3924,6 +3931,29 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF91B19-9A27-4376-8ED3-8B0A2484FC8F}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{7e753c2c-bb14-4786-921b-97c6a6fc424f}" enabled="1" method="Standard" siteId="{3bd97919-57c3-48d3-9e9a-8e4c01614a8f}" contentBits="2" removed="0"/>
